--- a/bioinformatics-analysis/resources/data-meta-en.xlsx
+++ b/bioinformatics-analysis/resources/data-meta-en.xlsx
@@ -1,172 +1,100 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="29005"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zwx/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="120" yWindow="5840" windowWidth="28680" windowHeight="8260"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="120" yWindow="5840" windowWidth="28680" windowHeight="8260" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="150001" concurrentCalc="0"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
-      <x14:workbookPr defaultImageDpi="32767"/>
-    </ext>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
-      <mx:ArchID Flags="2"/>
-    </ext>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="150001" fullCalcOnLoad="1" concurrentCalc="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>Data Details</t>
-  </si>
-  <si>
-    <t>Library Number</t>
-  </si>
-  <si>
-    <t>Index Type</t>
-  </si>
-  <si>
-    <t>Index Number</t>
-  </si>
-  <si>
-    <t>Hybrid Input (ng)</t>
-  </si>
-  <si>
-    <t>Type of Nucleic Acids</t>
-  </si>
-  <si>
-    <t>Degradation Grade of Nucleic Acids</t>
-  </si>
-  <si>
-    <t>Risk Sequencing</t>
-  </si>
-  <si>
-    <t>Capture Kit</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Library Construction Input(ng)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Nucleic Acid Fragmentation Method</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Submission Unit</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sample Identification Number</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Data Name Of R1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Data Name Of R2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="10" x14ac:knownFonts="1">
-    <font>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="10">
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
+      <charset val="134"/>
       <family val="2"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
       <charset val="134"/>
+      <family val="2"/>
+      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
-    </font>
-    <font>
+      <color theme="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="4"/>
+      <color theme="1"/>
       <sz val="21"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="18.850000000000001"/>
-      <color theme="1"/>
       <name val="Material Icons"/>
       <family val="1"/>
-    </font>
-    <font>
+      <color theme="1"/>
+      <sz val="18.85"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="4"/>
+      <color theme="1"/>
       <sz val="16"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Material Icons"/>
       <color theme="1"/>
+      <sz val="24"/>
+    </font>
+    <font>
       <name val="等线"/>
-      <family val="4"/>
       <charset val="134"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="24"/>
-      <color theme="1"/>
-      <name val="Material Icons"/>
-    </font>
-    <font>
-      <u/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <color theme="11"/>
       <sz val="11"/>
-      <color theme="10"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="11"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -181,63 +109,115 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+  <cellStyleXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="超链接" xfId="1" builtinId="8" hidden="1"/>
-    <cellStyle name="超链接" xfId="3" builtinId="8" hidden="1"/>
     <cellStyle name="已访问的超链接" xfId="2" builtinId="9" hidden="1"/>
-    <cellStyle name="已访问的超链接" xfId="4" builtinId="9" hidden="1"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -537,179 +517,220 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col width="10.33203125" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="12.33203125" bestFit="1" customWidth="1" style="7" min="8" max="8"/>
+    <col width="10.33203125" bestFit="1" customWidth="1" style="7" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="30" x14ac:dyDescent="0.2">
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="K2" s="6"/>
-      <c r="M2" s="2"/>
-    </row>
-    <row r="3" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="E3" s="5"/>
-    </row>
-    <row r="4" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="E4" s="5"/>
-      <c r="K4" s="5"/>
-    </row>
-    <row r="5" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="E5" s="5"/>
-      <c r="K5" s="5"/>
-    </row>
-    <row r="6" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="E6" s="5"/>
-      <c r="K6" s="5"/>
-    </row>
-    <row r="7" spans="1:15" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="3"/>
-      <c r="E7" s="5"/>
-      <c r="K7" s="5"/>
-    </row>
-    <row r="8" spans="1:15" ht="24" x14ac:dyDescent="0.2">
-      <c r="A8" s="4"/>
-    </row>
-    <row r="9" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="1:15" ht="30" x14ac:dyDescent="0.2">
-      <c r="A10" s="5"/>
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A11" s="5"/>
-    </row>
-    <row r="12" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A12" s="5"/>
-      <c r="E12" s="5"/>
-    </row>
-    <row r="13" spans="1:15" ht="30" x14ac:dyDescent="0.2">
-      <c r="A13" s="6"/>
-      <c r="E13" s="6"/>
-    </row>
-    <row r="14" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A14" s="5"/>
-    </row>
-    <row r="15" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A15" s="5"/>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A16" s="5"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="1:5" ht="21" x14ac:dyDescent="0.2">
-      <c r="A17" s="5"/>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="1:5" ht="21" x14ac:dyDescent="0.2">
-      <c r="A18" s="5"/>
-      <c r="E18" s="5"/>
-    </row>
-    <row r="19" spans="1:5" ht="21" x14ac:dyDescent="0.2">
-      <c r="A19" s="5"/>
-    </row>
-    <row r="20" spans="1:5" ht="21" x14ac:dyDescent="0.2">
-      <c r="A20" s="5"/>
-    </row>
-    <row r="22" spans="1:5" ht="21" x14ac:dyDescent="0.2">
-      <c r="A22" s="5"/>
-    </row>
-    <row r="23" spans="1:5" ht="30" x14ac:dyDescent="0.2">
-      <c r="A23" s="6"/>
-    </row>
-    <row r="25" spans="1:5" ht="21" x14ac:dyDescent="0.2">
-      <c r="A25" s="5"/>
-    </row>
-    <row r="26" spans="1:5" ht="30" x14ac:dyDescent="0.2">
-      <c r="A26" s="6"/>
-    </row>
-    <row r="28" spans="1:5" ht="21" x14ac:dyDescent="0.2">
-      <c r="A28" s="5"/>
-    </row>
-    <row r="29" spans="1:5" ht="21" x14ac:dyDescent="0.2">
-      <c r="A29" s="5"/>
-    </row>
-    <row r="30" spans="1:5" ht="21" x14ac:dyDescent="0.2">
-      <c r="A30" s="5"/>
-    </row>
-    <row r="31" spans="1:5" ht="21" x14ac:dyDescent="0.2">
-      <c r="A31" s="5"/>
+    <row r="1" ht="21" customHeight="1" s="7">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Data Details</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Library Number</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Capture Kit</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Library Construction Input(ng)</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Index Type</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Index Number</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Hybrid Input (ng)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Nucleic Acid Fragmentation Method</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Submission Unit</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Type of Nucleic Acids</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Degradation Grade of Nucleic Acids</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>Risk Sequencing</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Sample Identification Number</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Tag Label</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Data Name Of R1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Data Name Of R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" s="7">
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="K2" s="6" t="n"/>
+      <c r="M2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="21" customHeight="1" s="7">
+      <c r="E3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="21" customHeight="1" s="7">
+      <c r="E4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="21" customHeight="1" s="7">
+      <c r="E5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="21" customHeight="1" s="7">
+      <c r="E6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="27" customHeight="1" s="7">
+      <c r="A7" s="3" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1" s="7">
+      <c r="A8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="21" customHeight="1" s="7">
+      <c r="E9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1" s="7">
+      <c r="A10" s="5" t="n"/>
+      <c r="E10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="21" customHeight="1" s="7">
+      <c r="A11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="21" customHeight="1" s="7">
+      <c r="A12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="7">
+      <c r="A13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="21" customHeight="1" s="7">
+      <c r="A14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="21" customHeight="1" s="7">
+      <c r="A15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="21" customHeight="1" s="7">
+      <c r="A16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="21" customHeight="1" s="7">
+      <c r="A17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="21" customHeight="1" s="7">
+      <c r="A18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="21" customHeight="1" s="7">
+      <c r="A19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="21" customHeight="1" s="7">
+      <c r="A20" s="5" t="n"/>
+    </row>
+    <row r="21"/>
+    <row r="22" ht="21" customHeight="1" s="7">
+      <c r="A22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="30" customHeight="1" s="7">
+      <c r="A23" s="6" t="n"/>
+    </row>
+    <row r="24"/>
+    <row r="25" ht="21" customHeight="1" s="7">
+      <c r="A25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="30" customHeight="1" s="7">
+      <c r="A26" s="6" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28" ht="21" customHeight="1" s="7">
+      <c r="A28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="21" customHeight="1" s="7">
+      <c r="A29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="21" customHeight="1" s="7">
+      <c r="A30" s="5" t="n"/>
+    </row>
+    <row r="31" ht="21" customHeight="1" s="7">
+      <c r="A31" s="5" t="n"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576">
+    <dataValidation sqref="C2:C1048576" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>"Exome Plus Panel v2.0,HiSNP Panel v1.0,HiSNP Ultra Panel v1.0,HLAtyping Panel v1.0,NanOnco Plus Panel v3.0,OncoFu Elite V1.0,Methlyation panel V1.0,LungCancer Panel v1.0,NanOnCT Panel v1.0"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576">
+    <dataValidation sqref="J2:J1048576" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>"gDNA,cfDNA,RNA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K13:K1048576">
+    <dataValidation sqref="K13:K1048576" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>"A,B,C,D"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
+    <dataValidation sqref="D2:D1048576" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="decimal">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576">
+    <dataValidation sqref="G2:G1048576" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="decimal">
       <formula1>0</formula1>
       <formula2>99999999999999</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L1:L1048576">
+    <dataValidation sqref="L1:L1048576" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>

--- a/bioinformatics-analysis/resources/data-meta-en.xlsx
+++ b/bioinformatics-analysis/resources/data-meta-en.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
@@ -609,6 +609,11 @@
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Data Name Of R2</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr" s="1">
+        <is>
+          <t>MSRE</t>
         </is>
       </c>
     </row>
